--- a/Value_Stream_Data 1.xlsx
+++ b/Value_Stream_Data 1.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deepti.singh\OneDrive - The Knowledge Academy\work\Assigned Task folder\COURSEWARE\June 2026\DevOps Leader Interactive Training\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\training\DEVOPS LEADERS\Used_dataset___document\Used dataset &amp; document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_095AA95F1555FA6FE12418D7568BD67BCCE1E81A" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{07E46D7F-D0D3-4097-990A-BAEDAC8A1639}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618C80FA-EF62-4162-B205-24EAD562888E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12390" yWindow="-90" windowWidth="19380" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Value Stream" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Stage</t>
   </si>
@@ -83,6 +96,30 @@
   </si>
   <si>
     <t>Total Rework</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>Value added time</t>
+  </si>
+  <si>
+    <t>NVAT</t>
+  </si>
+  <si>
+    <t>None Value added time</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>per hour</t>
+  </si>
+  <si>
+    <t>per week</t>
+  </si>
+  <si>
+    <t>per day</t>
   </si>
 </sst>
 </file>
@@ -428,17 +465,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
+    <col min="3" max="4" width="17.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,13 +488,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -466,13 +508,16 @@
         <v>8</v>
       </c>
       <c r="D2">
+        <v>199</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -483,13 +528,16 @@
         <v>12</v>
       </c>
       <c r="D3">
+        <v>129</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -500,13 +548,16 @@
         <v>10</v>
       </c>
       <c r="D4">
+        <v>4888</v>
+      </c>
+      <c r="E4">
         <v>8</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -517,13 +568,16 @@
         <v>2</v>
       </c>
       <c r="D5">
+        <v>382</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -534,13 +588,16 @@
         <v>24</v>
       </c>
       <c r="D6">
+        <v>2828</v>
+      </c>
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -551,13 +608,16 @@
         <v>8</v>
       </c>
       <c r="D7">
+        <v>3833</v>
+      </c>
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -568,13 +628,16 @@
         <v>4</v>
       </c>
       <c r="D8">
+        <v>222</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -583,13 +646,74 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="D11">
-        <f>SUM(D2:D8)</f>
+      <c r="E11">
+        <f>SUM(E2:E8)</f>
         <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <f>1/B10</f>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="E13">
+        <f>24*D13</f>
+        <v>0.21818181818181817</v>
+      </c>
+      <c r="F13">
+        <f>E13*5</f>
+        <v>1.0909090909090908</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <f>SUM(B2:B8)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17">
+        <f>SUM(C2:C8)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="G19">
+        <f>(F16+F17)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <f>G19/F16</f>
+        <v>2.6190476190476191</v>
       </c>
     </row>
   </sheetData>
